--- a/artfynd/S 3321-2022 artfynd.xlsx
+++ b/artfynd/S 3321-2022 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>136137201</v>
       </c>
       <c r="B6" t="n">
-        <v>58262</v>
+        <v>58264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136137202</v>
       </c>
       <c r="B8" t="n">
-        <v>58594</v>
+        <v>58596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
